--- a/docs/referral-pricing/松山翼様ご紹介プラン_価格表.xlsx
+++ b/docs/referral-pricing/松山翼様ご紹介プラン_価格表.xlsx
@@ -363,7 +363,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">★仮置きの数値です。実際に松山様へお支払いしていた月額に必ず書き換えてください。
+          <t xml:space="preserve">★仮置きの数値です。実際に松山翼様へお支払いしていた月額に必ず書き換えてください。
 この</t>
         </r>
         <r>
@@ -391,7 +391,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="173">
   <si>
-    <t xml:space="preserve">松山様ご紹介プラン｜補綴（セラミック治療）価格表　※医院内部用・粗利つき</t>
+    <t xml:space="preserve">松山翼様ご紹介プラン｜補綴（セラミック治療）価格表　※医院内部用・粗利つき</t>
   </si>
   <si>
     <r>
@@ -552,7 +552,7 @@
     <t xml:space="preserve">【設定値】ここを変えると下表がすべて再計算されます（青字＝入力セル）</t>
   </si>
   <si>
-    <t xml:space="preserve">松山様ご紹介の割引率（補綴）</t>
+    <t xml:space="preserve">松山翼様ご紹介の割引率（補綴）</t>
   </si>
   <si>
     <t xml:space="preserve">← 当院の値引き下限。これ以上は下げない</t>
@@ -1152,7 +1152,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">列＝松山様ご紹介の方に提示する価格。</t>
+      <t xml:space="preserve">列＝松山翼様ご紹介の方に提示する価格。</t>
     </r>
     <r>
       <rPr>
@@ -1534,7 +1534,7 @@
     <t xml:space="preserve">◆ 実際の手取りは、上表の利益から消費税納税分と院内コストを引いた額になる。</t>
   </si>
   <si>
-    <t xml:space="preserve">松山様ご紹介プラン｜矯正（インビザライン）価格表　※医院内部用・粗利つき</t>
+    <t xml:space="preserve">松山翼様ご紹介プラン｜矯正（インビザライン）価格表　※医院内部用・粗利つき</t>
   </si>
   <si>
     <r>
@@ -2961,7 +2961,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円）。松山様紹介の症例は必ず</t>
+      <t xml:space="preserve">円）。松山翼様紹介の症例は必ず</t>
     </r>
     <r>
       <rPr>
@@ -2989,7 +2989,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">◆ 松山様から矯正の値引きを強く求められた場合の最終ラインは</t>
+      <t xml:space="preserve">◆ 松山翼様から矯正の値引きを強く求められた場合の最終ラインは</t>
     </r>
     <r>
       <rPr>
@@ -3246,7 +3246,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">【設定値】従来松山様に毎月お支払いしていた紹介料の実額を入れてください（青字＝入力セル）</t>
+    <t xml:space="preserve">【設定値】従来松山翼様に毎月お支払いしていた紹介料の実額を入れてください（青字＝入力セル）</t>
   </si>
   <si>
     <t xml:space="preserve">従来の月額紹介料（実額に置き換えてください）</t>
@@ -4507,10 +4507,10 @@
     <t xml:space="preserve">◆ そのかわり、紹介が想定以上に集中すると値引き総額が青天井になりうる。運用ルールのシートで月間上限・有効期限を必ず決めておくこと。</t>
   </si>
   <si>
-    <t xml:space="preserve">松山様ご紹介プラン｜運用ルールと確認事項</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配布用の価格表（松山様にお渡しする版）とセットで運用してください。以下は医院側の取り決めです。</t>
+    <t xml:space="preserve">松山翼様ご紹介プラン｜運用ルールと確認事項</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配布用の価格表（松山翼様にお渡しする版）とセットで運用してください。以下は医院側の取り決めです。</t>
   </si>
   <si>
     <r>
@@ -4534,10 +4534,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">◆ 対象＝松山様からのご紹介であれば誰でも。暁の城の在籍者に限定しない（院長決裁事項）。初診の受付時に「松山さんの紹介」と申告があった方。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">◆ 【重要】対象を「松山様の紹介」とする以上、店舗の在籍者に限定した場合より範囲は広い。紹介の連鎖も起こりうるため、月間上限と有効期限を必ずセットで決める。</t>
+    <t xml:space="preserve">◆ 対象＝松山翼様からのご紹介であれば誰でも。暁の城の在籍者に限定しない（院長決裁事項）。初診の受付時に「松山翼さんの紹介」と申告があった方。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◆ 【重要】対象を「松山翼様の紹介」とする以上、店舗の在籍者に限定した場合より範囲は広い。紹介の連鎖も起こりうるため、月間上限と有効期限を必ずセットで決める。</t>
   </si>
   <si>
     <t xml:space="preserve">◆ 【重要】自費診療のみが対象。保険診療の一部負担金は法令上、値引き・免除ができないため必ず対象外とする。</t>
@@ -4841,7 +4841,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">◆ 紹介カード（暁の城の名前入り）を渡す、または松山様からの</t>
+      <t xml:space="preserve">◆ 紹介カード（暁の城の名前入り）を渡す、または松山翼様からの</t>
     </r>
     <r>
       <rPr>
@@ -4879,7 +4879,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">◆ カルテまたは予約システムに「松山様紹介」のタグを付け、集計できるようにする。</t>
+    <t xml:space="preserve">◆ カルテまたは予約システムに「松山翼様紹介」のタグを付け、集計できるようにする。</t>
   </si>
   <si>
     <r>
@@ -4899,11 +4899,11 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">松山様への説明のしかた（ここが交渉のポイント）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">◆ 「紹介料をやめる」ではなく「紹介料を、ご紹介した方が直接受け取れる形に変える」という説明にする。松山様から見れば人に勧めやすい材料になる。</t>
+      <t xml:space="preserve">松山翼様への説明のしかた（ここが交渉のポイント）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">◆ 「紹介料をやめる」ではなく「紹介料を、ご紹介した方が直接受け取れる形に変える」という説明にする。松山翼様から見れば人に勧めやすい材料になる。</t>
   </si>
   <si>
     <r>
@@ -5011,7 +5011,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">◆ 松山様個人には現金が入らなくなる点は必ず正面から確認する。ここが合意できないと制度が続かない。</t>
+    <t xml:space="preserve">◆ 松山翼様個人には現金が入らなくなる点は必ず正面から確認する。ここが合意できないと制度が続かない。</t>
   </si>
   <si>
     <r>
@@ -5074,7 +5074,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">◆ 以前松山様とは別の提携先にお送りした </t>
+      <t xml:space="preserve">◆ 以前松山翼様とは別の提携先にお送りした </t>
     </r>
     <r>
       <rPr>
@@ -5123,7 +5123,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">◆ 従来松山様にお支払いしていた月額紹介料の実額も未共有のため、損益分岐シミュレーションでは仮に</t>
+      <t xml:space="preserve">◆ 従来松山翼様にお支払いしていた月額紹介料の実額も未共有のため、損益分岐シミュレーションでは仮に</t>
     </r>
     <r>
       <rPr>
